--- a/file/Aspire_Web_VPATJ00742.xlsx
+++ b/file/Aspire_Web_VPATJ00742.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87B68EB8-47B3-4812-AA97-110CDC096948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{019878BE-A71C-4F04-9DFF-45F1F9E95E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{C9AC6749-A600-4757-A761-AEC718238D7E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{8F2752BF-F63F-4564-B7DE-9D74FBC1F0FD}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -92,7 +92,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>7</t>
+      <t>8</t>
     </r>
     <r>
       <rPr>
@@ -111,7 +111,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>17</t>
+      <t>12</t>
     </r>
     <r>
       <rPr>
@@ -2604,7 +2604,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{608F1410-98FD-4E59-8F7C-ACA80BDD3983}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39BEE9B1-F77D-43E1-9F92-F8E7C19E99B9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3420,7 +3420,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14:E14" r:id="rId1" display="https://aspire.dev/" xr:uid="{DF296D8F-1D0F-44F6-86CE-E8606A2402E4}"/>
+    <hyperlink ref="B14:E14" r:id="rId1" display="https://aspire.dev/" xr:uid="{9BF7149D-7A96-4633-AF4C-92F783D08C8A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3428,7 +3428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C424223D-A1BB-489D-B14C-7EE00464654C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F20F1930-ABA9-42DA-860A-2B8DF296AB1E}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
